--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ts_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ts_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>05-06-2021 08:30</t>
+          <t>2021-05-06 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="n">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="n">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5085,7 +5085,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6795,7 +6795,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="n">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="n">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8886,7 +8886,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9795,7 +9795,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10906,7 +10906,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>09-10-2021 08:30</t>
+          <t>2021-09-10 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="n">
@@ -12320,7 +12320,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="n">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="n">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="n">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="n">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -12795,7 +12795,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12985,7 +12985,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -13080,7 +13080,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13650,7 +13650,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13745,7 +13745,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13840,7 +13840,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13935,7 +13935,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -14125,7 +14125,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14410,7 +14410,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14600,7 +14600,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15835,7 +15835,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="n">
@@ -16025,7 +16025,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="n">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="n">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="n">
@@ -16405,7 +16405,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="n">
@@ -16500,7 +16500,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="n">
@@ -16595,7 +16595,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="n">
@@ -16690,7 +16690,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="n">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="n">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="n">
@@ -16975,7 +16975,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="n">
@@ -17070,7 +17070,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="n">
@@ -17165,7 +17165,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="n">
@@ -17260,7 +17260,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="n">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="n">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="n">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="n">
@@ -17735,7 +17735,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="n">
@@ -17830,7 +17830,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="n">
@@ -17925,7 +17925,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="n">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="n">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="n">
@@ -18305,7 +18305,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="n">
@@ -18400,7 +18400,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="n">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="n">
@@ -18590,7 +18590,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18685,7 +18685,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="n">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="n">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="n">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="n">
@@ -19065,7 +19065,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="n">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="n">
@@ -19255,7 +19255,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="n">
@@ -19350,7 +19350,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19443,7 +19443,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19629,7 +19629,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19819,7 +19819,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -20009,7 +20009,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -20294,7 +20294,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20579,7 +20579,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20767,7 +20767,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -21046,7 +21046,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -21139,7 +21139,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -21325,7 +21325,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21418,7 +21418,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21511,7 +21511,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21604,7 +21604,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21697,7 +21697,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21790,7 +21790,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21883,7 +21883,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21976,7 +21976,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -22069,7 +22069,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -22162,7 +22162,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22255,7 +22255,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22348,7 +22348,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22441,7 +22441,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22627,7 +22627,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22720,7 +22720,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22813,7 +22813,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22906,7 +22906,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22999,7 +22999,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -23092,7 +23092,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -23185,7 +23185,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23278,7 +23278,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23371,7 +23371,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23464,7 +23464,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="n">
@@ -23652,7 +23652,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="n">
@@ -24032,7 +24032,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="n">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="n">
@@ -24222,7 +24222,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24317,7 +24317,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
@@ -24412,7 +24412,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="n">
@@ -24507,7 +24507,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="n">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="n">
@@ -24697,7 +24697,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="n">
@@ -24792,7 +24792,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="n">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="n">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="n">
@@ -25077,7 +25077,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="n">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="n">
@@ -25267,7 +25267,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="n">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="n">
@@ -25457,7 +25457,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="n">
@@ -25552,7 +25552,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="n">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="n">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="n">
@@ -25837,7 +25837,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="n">
@@ -25932,7 +25932,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="n">
@@ -26027,7 +26027,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="n">
@@ -26122,7 +26122,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="n">
@@ -26217,7 +26217,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="n">
@@ -26312,7 +26312,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="n">
@@ -26407,7 +26407,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="n">
@@ -26502,7 +26502,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="n">
@@ -26597,7 +26597,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="n">
@@ -26692,7 +26692,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="n">
@@ -26787,7 +26787,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="n">
@@ -26882,7 +26882,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="n">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="n">
@@ -27072,7 +27072,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="n">
@@ -27167,7 +27167,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="n">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="n">
@@ -27357,7 +27357,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="n">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27547,7 +27547,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27642,7 +27642,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27737,7 +27737,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27832,7 +27832,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27927,7 +27927,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -28022,7 +28022,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -28117,7 +28117,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -28212,7 +28212,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28307,7 +28307,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28402,7 +28402,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28592,7 +28592,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28687,7 +28687,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="inlineStr"/>
@@ -28780,7 +28780,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="inlineStr"/>
@@ -28873,7 +28873,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="inlineStr"/>
@@ -28966,7 +28966,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -29061,7 +29061,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -29156,7 +29156,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -29251,7 +29251,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29346,7 +29346,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29536,7 +29536,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29631,7 +29631,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29726,7 +29726,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -30201,7 +30201,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -30296,7 +30296,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30391,7 +30391,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>18-05-2021 08:30</t>
+          <t>2021-05-18 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>14-06-2021 08:30</t>
+          <t>2021-06-14 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30581,7 +30581,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="n">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="n">
@@ -30771,7 +30771,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="n">
@@ -30866,7 +30866,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="n">
@@ -30961,7 +30961,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="n">
@@ -31056,7 +31056,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="n">
@@ -31151,7 +31151,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="n">
@@ -31246,7 +31246,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="n">
@@ -31341,7 +31341,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="n">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="n">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="n">
@@ -31626,7 +31626,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="n">
@@ -31721,7 +31721,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="n">
@@ -31816,7 +31816,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>03-01-2021 08:30</t>
+          <t>2021-03-01 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31909,7 +31909,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -32002,7 +32002,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -32095,7 +32095,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="n">
@@ -32190,7 +32190,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="n">
@@ -32285,7 +32285,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="n">
@@ -32380,7 +32380,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="n">
@@ -32475,7 +32475,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="n">
@@ -32570,7 +32570,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="n">
@@ -32665,7 +32665,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="n">
@@ -32760,7 +32760,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="n">
@@ -32855,7 +32855,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="n">
@@ -32950,7 +32950,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="n">
@@ -33045,7 +33045,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>12-11-2021 08:30</t>
+          <t>2021-12-11 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="n">
@@ -33140,7 +33140,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="n">
@@ -33235,7 +33235,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="n">
@@ -33330,7 +33330,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="n">
@@ -33425,7 +33425,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="n">
@@ -33520,7 +33520,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="n">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="n">
@@ -33710,7 +33710,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="n">
@@ -33805,7 +33805,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="n">
@@ -33900,7 +33900,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="n">
@@ -33995,7 +33995,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="n">
@@ -34090,7 +34090,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="n">
@@ -34185,7 +34185,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -34280,7 +34280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34375,7 +34375,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34470,7 +34470,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34565,7 +34565,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34660,7 +34660,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34755,7 +34755,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34850,7 +34850,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34945,7 +34945,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="n">
@@ -35040,7 +35040,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="n">
@@ -35135,7 +35135,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="n">
@@ -35230,7 +35230,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>11-11-2021 08:30</t>
+          <t>2021-11-11 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="n">
@@ -35325,7 +35325,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="n">
@@ -35420,7 +35420,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="n">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T367" t="n">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T368" t="n">
@@ -35705,7 +35705,7 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T369" t="n">
@@ -35800,7 +35800,7 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T370" t="n">
@@ -35895,7 +35895,7 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T371" t="n">
@@ -35990,7 +35990,7 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T372" t="n">
@@ -36085,7 +36085,7 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T373" t="n">
@@ -36180,7 +36180,7 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T374" t="n">
@@ -36275,7 +36275,7 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T375" t="n">
@@ -36370,7 +36370,7 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T376" t="n">
@@ -36465,7 +36465,7 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T377" t="n">
@@ -36560,7 +36560,7 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T378" t="n">
@@ -36655,7 +36655,7 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T379" t="n">
@@ -36750,7 +36750,7 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T380" t="n">
@@ -36845,7 +36845,7 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T381" t="n">
@@ -36940,7 +36940,7 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T382" t="n">
@@ -37035,7 +37035,7 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T383" t="n">
@@ -37130,7 +37130,7 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T384" t="n">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T385" t="n">
@@ -37320,7 +37320,7 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T386" t="n">
@@ -37415,7 +37415,7 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T387" t="n">
@@ -37510,7 +37510,7 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T388" t="inlineStr"/>
@@ -37603,7 +37603,7 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T389" t="inlineStr"/>
@@ -37696,7 +37696,7 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T390" t="inlineStr"/>
@@ -37789,7 +37789,7 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T391" t="n">
@@ -37884,7 +37884,7 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T392" t="n">
@@ -37979,7 +37979,7 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T393" t="n">
@@ -38074,7 +38074,7 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T394" t="n">
@@ -38169,7 +38169,7 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T395" t="n">
@@ -38264,7 +38264,7 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T396" t="n">
@@ -38359,7 +38359,7 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T397" t="n">
@@ -38454,7 +38454,7 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T398" t="n">
@@ -38549,7 +38549,7 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T399" t="n">
@@ -38644,7 +38644,7 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T400" t="n">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T401" t="n">
@@ -38834,7 +38834,7 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T402" t="n">
@@ -38929,7 +38929,7 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T403" t="n">
@@ -39024,7 +39024,7 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T404" t="n">
@@ -39119,7 +39119,7 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T405" t="n">
@@ -39214,7 +39214,7 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T406" t="n">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T407" t="n">
@@ -39404,7 +39404,7 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T408" t="n">
@@ -39499,7 +39499,7 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T409" t="n">
@@ -39594,7 +39594,7 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T410" t="n">
@@ -39689,7 +39689,7 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T411" t="n">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T412" t="n">
@@ -39879,7 +39879,7 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T413" t="n">
@@ -39974,7 +39974,7 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T414" t="n">
@@ -40069,7 +40069,7 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T415" t="n">
@@ -40164,7 +40164,7 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T416" t="n">
@@ -40259,7 +40259,7 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T417" t="n">
@@ -40354,7 +40354,7 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T418" t="n">
@@ -40449,7 +40449,7 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T419" t="n">
@@ -40544,7 +40544,7 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T420" t="n">
@@ -40639,7 +40639,7 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T421" t="n">
@@ -40734,7 +40734,7 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T422" t="n">
@@ -40829,7 +40829,7 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T423" t="n">
@@ -40924,7 +40924,7 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T424" t="n">
@@ -41019,7 +41019,7 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T425" t="n">
@@ -41114,7 +41114,7 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T426" t="n">
@@ -41209,7 +41209,7 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T427" t="n">
@@ -41304,7 +41304,7 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T428" t="n">
@@ -41399,7 +41399,7 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T429" t="n">
@@ -41494,7 +41494,7 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T430" t="n">
@@ -41589,7 +41589,7 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T431" t="n">
@@ -41684,7 +41684,7 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T432" t="n">
@@ -41779,7 +41779,7 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T433" t="n">
@@ -41874,7 +41874,7 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T434" t="n">
@@ -41969,7 +41969,7 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T435" t="n">
@@ -42064,7 +42064,7 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T436" t="n">
@@ -42159,7 +42159,7 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T437" t="n">
@@ -42254,7 +42254,7 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T438" t="n">
@@ -42349,7 +42349,7 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T439" t="n">
@@ -42444,7 +42444,7 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T440" t="n">
@@ -42539,7 +42539,7 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T441" t="n">
@@ -42634,7 +42634,7 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T442" t="n">
@@ -42729,7 +42729,7 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T443" t="n">
@@ -42824,7 +42824,7 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T444" t="n">
@@ -42919,7 +42919,7 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T445" t="n">
@@ -43014,7 +43014,7 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T446" t="inlineStr"/>
@@ -43107,7 +43107,7 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T447" t="inlineStr"/>
@@ -43200,7 +43200,7 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T448" t="inlineStr"/>
@@ -43293,7 +43293,7 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T449" t="n">
@@ -43388,7 +43388,7 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T450" t="n">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T451" t="n">
@@ -43578,7 +43578,7 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T452" t="n">
@@ -43673,7 +43673,7 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T453" t="n">
@@ -43768,7 +43768,7 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T454" t="n">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T455" t="n">
@@ -43958,7 +43958,7 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T456" t="n">
@@ -44053,7 +44053,7 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T457" t="n">
@@ -44148,7 +44148,7 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T458" t="n">
@@ -44243,7 +44243,7 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T459" t="n">
@@ -44338,7 +44338,7 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T460" t="n">
@@ -44433,7 +44433,7 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T461" t="n">
@@ -44528,7 +44528,7 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T462" t="n">
@@ -44623,7 +44623,7 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T463" t="n">
@@ -44718,7 +44718,7 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T464" t="n">
@@ -44813,7 +44813,7 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T465" t="n">
@@ -44908,7 +44908,7 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T466" t="n">
@@ -45003,7 +45003,7 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T467" t="n">
@@ -45098,7 +45098,7 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T468" t="n">
@@ -45193,7 +45193,7 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T469" t="n">
@@ -45288,7 +45288,7 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T470" t="n">
@@ -45383,7 +45383,7 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T471" t="n">
@@ -45478,7 +45478,7 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T472" t="n">
@@ -45573,7 +45573,7 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T473" t="n">
@@ -45668,7 +45668,7 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T474" t="n">
@@ -45763,7 +45763,7 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T475" t="inlineStr"/>
@@ -45856,7 +45856,7 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T476" t="inlineStr"/>
@@ -45949,7 +45949,7 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T477" t="inlineStr"/>
@@ -46042,7 +46042,7 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T478" t="inlineStr"/>
@@ -46135,7 +46135,7 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T479" t="inlineStr"/>
@@ -46228,7 +46228,7 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T480" t="inlineStr"/>
@@ -46321,7 +46321,7 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T481" t="inlineStr"/>
@@ -46414,7 +46414,7 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T482" t="inlineStr"/>
@@ -46507,7 +46507,7 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T483" t="inlineStr"/>
@@ -46600,7 +46600,7 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T484" t="inlineStr"/>
@@ -46693,7 +46693,7 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T485" t="inlineStr"/>
@@ -46786,7 +46786,7 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T486" t="inlineStr"/>
@@ -46879,7 +46879,7 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T487" t="inlineStr"/>
@@ -46972,7 +46972,7 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T488" t="inlineStr"/>
@@ -47065,7 +47065,7 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T489" t="inlineStr"/>
@@ -47158,7 +47158,7 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T490" t="n">
@@ -47253,7 +47253,7 @@
       </c>
       <c r="S491" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T491" t="n">
@@ -47348,7 +47348,7 @@
       </c>
       <c r="S492" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T492" t="n">
@@ -47443,7 +47443,7 @@
       </c>
       <c r="S493" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T493" t="n">
@@ -47538,7 +47538,7 @@
       </c>
       <c r="S494" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T494" t="n">
@@ -47633,7 +47633,7 @@
       </c>
       <c r="S495" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T495" t="n">
@@ -47728,7 +47728,7 @@
       </c>
       <c r="S496" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T496" t="n">
@@ -47823,7 +47823,7 @@
       </c>
       <c r="S497" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T497" t="n">
@@ -47918,7 +47918,7 @@
       </c>
       <c r="S498" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T498" t="n">
@@ -48013,7 +48013,7 @@
       </c>
       <c r="S499" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T499" t="n">
@@ -48108,7 +48108,7 @@
       </c>
       <c r="S500" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T500" t="n">
@@ -48203,7 +48203,7 @@
       </c>
       <c r="S501" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T501" t="n">
@@ -48298,7 +48298,7 @@
       </c>
       <c r="S502" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T502" t="n">
@@ -48393,7 +48393,7 @@
       </c>
       <c r="S503" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T503" t="n">
@@ -48488,7 +48488,7 @@
       </c>
       <c r="S504" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T504" t="n">
@@ -48583,7 +48583,7 @@
       </c>
       <c r="S505" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T505" t="n">
@@ -48678,7 +48678,7 @@
       </c>
       <c r="S506" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T506" t="n">
@@ -48773,7 +48773,7 @@
       </c>
       <c r="S507" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T507" t="n">
@@ -48868,7 +48868,7 @@
       </c>
       <c r="S508" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T508" t="n">
@@ -48963,7 +48963,7 @@
       </c>
       <c r="S509" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T509" t="n">
@@ -49058,7 +49058,7 @@
       </c>
       <c r="S510" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T510" t="n">
@@ -49153,7 +49153,7 @@
       </c>
       <c r="S511" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T511" t="n">
@@ -49248,7 +49248,7 @@
       </c>
       <c r="S512" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T512" t="n">
@@ -49343,7 +49343,7 @@
       </c>
       <c r="S513" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T513" t="n">
@@ -49438,7 +49438,7 @@
       </c>
       <c r="S514" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T514" t="n">
@@ -49533,7 +49533,7 @@
       </c>
       <c r="S515" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T515" t="n">
@@ -49628,7 +49628,7 @@
       </c>
       <c r="S516" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T516" t="n">
@@ -49723,7 +49723,7 @@
       </c>
       <c r="S517" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T517" t="n">
@@ -49818,7 +49818,7 @@
       </c>
       <c r="S518" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T518" t="n">
@@ -49913,7 +49913,7 @@
       </c>
       <c r="S519" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T519" t="n">
@@ -50008,7 +50008,7 @@
       </c>
       <c r="S520" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T520" t="n">
@@ -50103,7 +50103,7 @@
       </c>
       <c r="S521" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T521" t="n">
@@ -50198,7 +50198,7 @@
       </c>
       <c r="S522" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T522" t="inlineStr"/>
@@ -50291,7 +50291,7 @@
       </c>
       <c r="S523" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T523" t="inlineStr"/>
@@ -50384,7 +50384,7 @@
       </c>
       <c r="S524" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T524" t="inlineStr"/>
@@ -50477,7 +50477,7 @@
       </c>
       <c r="S525" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T525" t="inlineStr"/>
@@ -50570,7 +50570,7 @@
       </c>
       <c r="S526" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T526" t="inlineStr"/>
@@ -50663,7 +50663,7 @@
       </c>
       <c r="S527" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T527" t="inlineStr"/>
@@ -50756,7 +50756,7 @@
       </c>
       <c r="S528" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T528" t="inlineStr"/>
@@ -50849,7 +50849,7 @@
       </c>
       <c r="S529" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T529" t="inlineStr"/>
@@ -50942,7 +50942,7 @@
       </c>
       <c r="S530" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T530" t="inlineStr"/>
@@ -51035,7 +51035,7 @@
       </c>
       <c r="S531" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T531" t="inlineStr"/>
@@ -51128,7 +51128,7 @@
       </c>
       <c r="S532" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T532" t="inlineStr"/>
@@ -51221,7 +51221,7 @@
       </c>
       <c r="S533" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T533" t="inlineStr"/>
@@ -51314,7 +51314,7 @@
       </c>
       <c r="S534" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T534" t="n">
@@ -51409,7 +51409,7 @@
       </c>
       <c r="S535" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T535" t="n">
@@ -51504,7 +51504,7 @@
       </c>
       <c r="S536" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T536" t="n">
@@ -51599,7 +51599,7 @@
       </c>
       <c r="S537" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T537" t="n">
@@ -51694,7 +51694,7 @@
       </c>
       <c r="S538" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T538" t="n">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="S539" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T539" t="n">
@@ -51884,7 +51884,7 @@
       </c>
       <c r="S540" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T540" t="n">
@@ -51979,7 +51979,7 @@
       </c>
       <c r="S541" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T541" t="n">
@@ -52074,7 +52074,7 @@
       </c>
       <c r="S542" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T542" t="n">
@@ -52169,7 +52169,7 @@
       </c>
       <c r="S543" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T543" t="n">
@@ -52264,7 +52264,7 @@
       </c>
       <c r="S544" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T544" t="n">
@@ -52359,7 +52359,7 @@
       </c>
       <c r="S545" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T545" t="n">
@@ -52454,7 +52454,7 @@
       </c>
       <c r="S546" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T546" t="n">
@@ -52549,7 +52549,7 @@
       </c>
       <c r="S547" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T547" t="n">
@@ -52644,7 +52644,7 @@
       </c>
       <c r="S548" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T548" t="n">
@@ -52739,7 +52739,7 @@
       </c>
       <c r="S549" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T549" t="n">
@@ -52834,7 +52834,7 @@
       </c>
       <c r="S550" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T550" t="n">
@@ -52929,7 +52929,7 @@
       </c>
       <c r="S551" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T551" t="n">
@@ -53024,7 +53024,7 @@
       </c>
       <c r="S552" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T552" t="inlineStr"/>
@@ -53117,7 +53117,7 @@
       </c>
       <c r="S553" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T553" t="inlineStr"/>
@@ -53210,7 +53210,7 @@
       </c>
       <c r="S554" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T554" t="inlineStr"/>
@@ -53303,7 +53303,7 @@
       </c>
       <c r="S555" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T555" t="n">
@@ -53398,7 +53398,7 @@
       </c>
       <c r="S556" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T556" t="n">
@@ -53493,7 +53493,7 @@
       </c>
       <c r="S557" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T557" t="n">
@@ -53588,7 +53588,7 @@
       </c>
       <c r="S558" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T558" t="n">
@@ -53683,7 +53683,7 @@
       </c>
       <c r="S559" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T559" t="n">
@@ -53778,7 +53778,7 @@
       </c>
       <c r="S560" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T560" t="n">
@@ -53873,7 +53873,7 @@
       </c>
       <c r="S561" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T561" t="n">
@@ -53968,7 +53968,7 @@
       </c>
       <c r="S562" t="inlineStr">
         <is>
-          <t>03-04-2021 08:30</t>
+          <t>2021-03-04 08:30:00</t>
         </is>
       </c>
       <c r="T562" t="n">
@@ -54063,7 +54063,7 @@
       </c>
       <c r="S563" t="inlineStr">
         <is>
-          <t>01-05-2021 08:30</t>
+          <t>2021-01-05 08:30:00</t>
         </is>
       </c>
       <c r="T563" t="n">
@@ -54158,7 +54158,7 @@
       </c>
       <c r="S564" t="inlineStr">
         <is>
-          <t>05-06-2021 08:30</t>
+          <t>2021-05-06 08:30:00</t>
         </is>
       </c>
       <c r="T564" t="n">
@@ -54253,7 +54253,7 @@
       </c>
       <c r="S565" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T565" t="n">
@@ -54348,7 +54348,7 @@
       </c>
       <c r="S566" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T566" t="n">
@@ -54443,7 +54443,7 @@
       </c>
       <c r="S567" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T567" t="n">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="S568" t="inlineStr">
         <is>
-          <t>06-11-2021 08:30</t>
+          <t>2021-06-11 08:30:00</t>
         </is>
       </c>
       <c r="T568" t="n">
@@ -54633,7 +54633,7 @@
       </c>
       <c r="S569" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T569" t="n">
@@ -54728,7 +54728,7 @@
       </c>
       <c r="S570" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T570" t="n">
@@ -54823,7 +54823,7 @@
       </c>
       <c r="S571" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T571" t="n">
@@ -54918,7 +54918,7 @@
       </c>
       <c r="S572" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T572" t="n">
@@ -55013,7 +55013,7 @@
       </c>
       <c r="S573" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T573" t="n">
@@ -55108,7 +55108,7 @@
       </c>
       <c r="S574" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T574" t="n">
@@ -55203,7 +55203,7 @@
       </c>
       <c r="S575" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T575" t="n">
@@ -55298,7 +55298,7 @@
       </c>
       <c r="S576" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T576" t="n">
@@ -55393,7 +55393,7 @@
       </c>
       <c r="S577" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T577" t="n">
@@ -55488,7 +55488,7 @@
       </c>
       <c r="S578" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T578" t="n">
@@ -55583,7 +55583,7 @@
       </c>
       <c r="S579" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T579" t="n">
@@ -55678,7 +55678,7 @@
       </c>
       <c r="S580" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T580" t="n">
@@ -55773,7 +55773,7 @@
       </c>
       <c r="S581" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T581" t="n">
@@ -55868,7 +55868,7 @@
       </c>
       <c r="S582" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T582" t="n">
@@ -55963,7 +55963,7 @@
       </c>
       <c r="S583" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T583" t="n">
@@ -56058,7 +56058,7 @@
       </c>
       <c r="S584" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T584" t="n">
@@ -56153,7 +56153,7 @@
       </c>
       <c r="S585" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T585" t="n">
@@ -56248,7 +56248,7 @@
       </c>
       <c r="S586" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T586" t="n">
@@ -56343,7 +56343,7 @@
       </c>
       <c r="S587" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T587" t="n">
@@ -56438,7 +56438,7 @@
       </c>
       <c r="S588" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T588" t="n">
@@ -56533,7 +56533,7 @@
       </c>
       <c r="S589" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T589" t="n">
@@ -56628,7 +56628,7 @@
       </c>
       <c r="S590" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T590" t="n">
@@ -56723,7 +56723,7 @@
       </c>
       <c r="S591" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T591" t="n">
@@ -56818,7 +56818,7 @@
       </c>
       <c r="S592" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T592" t="inlineStr"/>
@@ -56911,7 +56911,7 @@
       </c>
       <c r="S593" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T593" t="inlineStr"/>
@@ -57004,7 +57004,7 @@
       </c>
       <c r="S594" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T594" t="inlineStr"/>
@@ -57097,7 +57097,7 @@
       </c>
       <c r="S595" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T595" t="inlineStr"/>
@@ -57190,7 +57190,7 @@
       </c>
       <c r="S596" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T596" t="inlineStr"/>
@@ -57283,7 +57283,7 @@
       </c>
       <c r="S597" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T597" t="inlineStr"/>
@@ -57376,7 +57376,7 @@
       </c>
       <c r="S598" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T598" t="inlineStr"/>
@@ -57469,7 +57469,7 @@
       </c>
       <c r="S599" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T599" t="inlineStr"/>
@@ -57562,7 +57562,7 @@
       </c>
       <c r="S600" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T600" t="inlineStr"/>
@@ -57655,7 +57655,7 @@
       </c>
       <c r="S601" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T601" t="n">
@@ -57756,7 +57756,7 @@
       </c>
       <c r="S602" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T602" t="n">
@@ -57857,7 +57857,7 @@
       </c>
       <c r="S603" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T603" t="inlineStr"/>
@@ -57950,7 +57950,7 @@
       </c>
       <c r="S604" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T604" t="inlineStr"/>
@@ -58043,7 +58043,7 @@
       </c>
       <c r="S605" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T605" t="inlineStr"/>
@@ -58136,7 +58136,7 @@
       </c>
       <c r="S606" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T606" t="n">
@@ -58231,7 +58231,7 @@
       </c>
       <c r="S607" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T607" t="n">
@@ -58326,7 +58326,7 @@
       </c>
       <c r="S608" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T608" t="n">
@@ -58421,7 +58421,7 @@
       </c>
       <c r="S609" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T609" t="n">
@@ -58516,7 +58516,7 @@
       </c>
       <c r="S610" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T610" t="n">
@@ -58611,7 +58611,7 @@
       </c>
       <c r="S611" t="inlineStr">
         <is>
-          <t>21-06-2021 08:30</t>
+          <t>2021-06-21 08:30:00</t>
         </is>
       </c>
       <c r="T611" t="n">
@@ -58706,7 +58706,7 @@
       </c>
       <c r="S612" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T612" t="n">
@@ -58801,7 +58801,7 @@
       </c>
       <c r="S613" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T613" t="n">
@@ -58896,7 +58896,7 @@
       </c>
       <c r="S614" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T614" t="n">
@@ -58991,7 +58991,7 @@
       </c>
       <c r="S615" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T615" t="n">
@@ -59086,7 +59086,7 @@
       </c>
       <c r="S616" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T616" t="n">
@@ -59181,7 +59181,7 @@
       </c>
       <c r="S617" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T617" t="inlineStr"/>
@@ -59274,7 +59274,7 @@
       </c>
       <c r="S618" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T618" t="inlineStr"/>
@@ -59367,7 +59367,7 @@
       </c>
       <c r="S619" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T619" t="inlineStr"/>
@@ -59460,7 +59460,7 @@
       </c>
       <c r="S620" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T620" t="n">
@@ -59555,7 +59555,7 @@
       </c>
       <c r="S621" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T621" t="n">
@@ -59650,7 +59650,7 @@
       </c>
       <c r="S622" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T622" t="n">
@@ -59745,7 +59745,7 @@
       </c>
       <c r="S623" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T623" t="n">
@@ -59840,7 +59840,7 @@
       </c>
       <c r="S624" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T624" t="n">
@@ -59935,7 +59935,7 @@
       </c>
       <c r="S625" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T625" t="n">
@@ -60030,7 +60030,7 @@
       </c>
       <c r="S626" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T626" t="n">
@@ -60125,7 +60125,7 @@
       </c>
       <c r="S627" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T627" t="n">
@@ -60220,7 +60220,7 @@
       </c>
       <c r="S628" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T628" t="n">
@@ -60315,7 +60315,7 @@
       </c>
       <c r="S629" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T629" t="n">
@@ -60410,7 +60410,7 @@
       </c>
       <c r="S630" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T630" t="n">
@@ -60505,7 +60505,7 @@
       </c>
       <c r="S631" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T631" t="inlineStr"/>
@@ -60598,7 +60598,7 @@
       </c>
       <c r="S632" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T632" t="inlineStr"/>
@@ -60691,7 +60691,7 @@
       </c>
       <c r="S633" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T633" t="inlineStr"/>
@@ -60784,7 +60784,7 @@
       </c>
       <c r="S634" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T634" t="n">
@@ -60879,7 +60879,7 @@
       </c>
       <c r="S635" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T635" t="n">
@@ -60974,7 +60974,7 @@
       </c>
       <c r="S636" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T636" t="n">
@@ -61069,7 +61069,7 @@
       </c>
       <c r="S637" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T637" t="n">
@@ -61164,7 +61164,7 @@
       </c>
       <c r="S638" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T638" t="n">
@@ -61259,7 +61259,7 @@
       </c>
       <c r="S639" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T639" t="n">
@@ -61354,7 +61354,7 @@
       </c>
       <c r="S640" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T640" t="n">
@@ -61449,7 +61449,7 @@
       </c>
       <c r="S641" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T641" t="n">
@@ -61544,7 +61544,7 @@
       </c>
       <c r="S642" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T642" t="n">
@@ -61639,7 +61639,7 @@
       </c>
       <c r="S643" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T643" t="n">
@@ -61734,7 +61734,7 @@
       </c>
       <c r="S644" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T644" t="n">
@@ -61829,7 +61829,7 @@
       </c>
       <c r="S645" t="inlineStr">
         <is>
-          <t>24-03-2021 08:30</t>
+          <t>2021-03-24 08:30:00</t>
         </is>
       </c>
       <c r="T645" t="n">
@@ -61924,7 +61924,7 @@
       </c>
       <c r="S646" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T646" t="n">
@@ -62019,7 +62019,7 @@
       </c>
       <c r="S647" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T647" t="n">
@@ -62114,7 +62114,7 @@
       </c>
       <c r="S648" t="inlineStr">
         <is>
-          <t>22-06-2021 08:30</t>
+          <t>2021-06-22 08:30:00</t>
         </is>
       </c>
       <c r="T648" t="n">
@@ -62209,7 +62209,7 @@
       </c>
       <c r="S649" t="inlineStr">
         <is>
-          <t>10-07-2021 08:30</t>
+          <t>2021-10-07 08:30:00</t>
         </is>
       </c>
       <c r="T649" t="n">
@@ -62304,7 +62304,7 @@
       </c>
       <c r="S650" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T650" t="n">
@@ -62399,7 +62399,7 @@
       </c>
       <c r="S651" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T651" t="n">
@@ -62494,7 +62494,7 @@
       </c>
       <c r="S652" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T652" t="n">
@@ -62589,7 +62589,7 @@
       </c>
       <c r="S653" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T653" t="n">
@@ -62684,7 +62684,7 @@
       </c>
       <c r="S654" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T654" t="n">
@@ -62779,7 +62779,7 @@
       </c>
       <c r="S655" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T655" t="n">
@@ -62874,7 +62874,7 @@
       </c>
       <c r="S656" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T656" t="n">
@@ -62969,7 +62969,7 @@
       </c>
       <c r="S657" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T657" t="n">
@@ -63064,7 +63064,7 @@
       </c>
       <c r="S658" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T658" t="n">
@@ -63159,7 +63159,7 @@
       </c>
       <c r="S659" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T659" t="n">
@@ -63254,7 +63254,7 @@
       </c>
       <c r="S660" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T660" t="n">
@@ -63349,7 +63349,7 @@
       </c>
       <c r="S661" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T661" t="n">
@@ -63444,7 +63444,7 @@
       </c>
       <c r="S662" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T662" t="n">
@@ -63539,7 +63539,7 @@
       </c>
       <c r="S663" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T663" t="n">
@@ -63634,7 +63634,7 @@
       </c>
       <c r="S664" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T664" t="n">
@@ -63729,7 +63729,7 @@
       </c>
       <c r="S665" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T665" t="n">
@@ -63824,7 +63824,7 @@
       </c>
       <c r="S666" t="inlineStr">
         <is>
-          <t>28-01-2021 08:30</t>
+          <t>2021-01-28 08:30:00</t>
         </is>
       </c>
       <c r="T666" t="n">
@@ -63919,7 +63919,7 @@
       </c>
       <c r="S667" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T667" t="n">
@@ -64014,7 +64014,7 @@
       </c>
       <c r="S668" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T668" t="n">
@@ -64109,7 +64109,7 @@
       </c>
       <c r="S669" t="inlineStr">
         <is>
-          <t>15-04-2021 08:30</t>
+          <t>2021-04-15 08:30:00</t>
         </is>
       </c>
       <c r="T669" t="n">
@@ -64204,7 +64204,7 @@
       </c>
       <c r="S670" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T670" t="n">
@@ -64299,7 +64299,7 @@
       </c>
       <c r="S671" t="inlineStr">
         <is>
-          <t>19-06-2021 08:30</t>
+          <t>2021-06-19 08:30:00</t>
         </is>
       </c>
       <c r="T671" t="n">
@@ -64394,7 +64394,7 @@
       </c>
       <c r="S672" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T672" t="n">
@@ -64489,7 +64489,7 @@
       </c>
       <c r="S673" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T673" t="n">
@@ -64584,7 +64584,7 @@
       </c>
       <c r="S674" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T674" t="n">
@@ -64679,7 +64679,7 @@
       </c>
       <c r="S675" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T675" t="n">
@@ -64774,7 +64774,7 @@
       </c>
       <c r="S676" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T676" t="n">
@@ -64869,7 +64869,7 @@
       </c>
       <c r="S677" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T677" t="inlineStr"/>
@@ -64962,7 +64962,7 @@
       </c>
       <c r="S678" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T678" t="inlineStr"/>
@@ -65055,7 +65055,7 @@
       </c>
       <c r="S679" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T679" t="inlineStr"/>
@@ -65148,7 +65148,7 @@
       </c>
       <c r="S680" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T680" t="inlineStr"/>
@@ -65241,7 +65241,7 @@
       </c>
       <c r="S681" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T681" t="inlineStr"/>
@@ -65334,7 +65334,7 @@
       </c>
       <c r="S682" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T682" t="inlineStr"/>
@@ -65427,7 +65427,7 @@
       </c>
       <c r="S683" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T683" t="inlineStr"/>
@@ -65520,7 +65520,7 @@
       </c>
       <c r="S684" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T684" t="inlineStr"/>
@@ -65613,7 +65613,7 @@
       </c>
       <c r="S685" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T685" t="inlineStr"/>
@@ -65706,7 +65706,7 @@
       </c>
       <c r="S686" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T686" t="inlineStr"/>
@@ -65799,7 +65799,7 @@
       </c>
       <c r="S687" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T687" t="inlineStr"/>
@@ -65892,7 +65892,7 @@
       </c>
       <c r="S688" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T688" t="inlineStr"/>
@@ -65985,7 +65985,7 @@
       </c>
       <c r="S689" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T689" t="inlineStr"/>
@@ -66078,7 +66078,7 @@
       </c>
       <c r="S690" t="inlineStr">
         <is>
-          <t>06-02-2021 08:30</t>
+          <t>2021-06-02 08:30:00</t>
         </is>
       </c>
       <c r="T690" t="inlineStr"/>
@@ -66171,7 +66171,7 @@
       </c>
       <c r="S691" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T691" t="inlineStr"/>
@@ -66264,7 +66264,7 @@
       </c>
       <c r="S692" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T692" t="inlineStr"/>
@@ -66357,7 +66357,7 @@
       </c>
       <c r="S693" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T693" t="inlineStr"/>
@@ -66450,7 +66450,7 @@
       </c>
       <c r="S694" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T694" t="inlineStr"/>
@@ -66543,7 +66543,7 @@
       </c>
       <c r="S695" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T695" t="inlineStr"/>
@@ -66636,7 +66636,7 @@
       </c>
       <c r="S696" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T696" t="inlineStr"/>
@@ -66729,7 +66729,7 @@
       </c>
       <c r="S697" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T697" t="inlineStr"/>
@@ -66822,7 +66822,7 @@
       </c>
       <c r="S698" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T698" t="inlineStr"/>
@@ -66915,7 +66915,7 @@
       </c>
       <c r="S699" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T699" t="inlineStr"/>
@@ -67008,7 +67008,7 @@
       </c>
       <c r="S700" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T700" t="inlineStr"/>
@@ -67101,7 +67101,7 @@
       </c>
       <c r="S701" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T701" t="n">
@@ -67196,7 +67196,7 @@
       </c>
       <c r="S702" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T702" t="n">
@@ -67291,7 +67291,7 @@
       </c>
       <c r="S703" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T703" t="n">
@@ -67386,7 +67386,7 @@
       </c>
       <c r="S704" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T704" t="n">
@@ -67481,7 +67481,7 @@
       </c>
       <c r="S705" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T705" t="n">
@@ -67576,7 +67576,7 @@
       </c>
       <c r="S706" t="inlineStr">
         <is>
-          <t>17-06-2021 08:30</t>
+          <t>2021-06-17 08:30:00</t>
         </is>
       </c>
       <c r="T706" t="n">
@@ -67671,7 +67671,7 @@
       </c>
       <c r="S707" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T707" t="n">
@@ -67766,7 +67766,7 @@
       </c>
       <c r="S708" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T708" t="n">
@@ -67861,7 +67861,7 @@
       </c>
       <c r="S709" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T709" t="n">
@@ -67956,7 +67956,7 @@
       </c>
       <c r="S710" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T710" t="n">
@@ -68051,7 +68051,7 @@
       </c>
       <c r="S711" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T711" t="n">
@@ -68146,7 +68146,7 @@
       </c>
       <c r="S712" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T712" t="n">
@@ -68241,7 +68241,7 @@
       </c>
       <c r="S713" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T713" t="n">
@@ -68336,7 +68336,7 @@
       </c>
       <c r="S714" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T714" t="n">
@@ -68431,7 +68431,7 @@
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T715" t="n">
@@ -68526,7 +68526,7 @@
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T716" t="n">
@@ -68621,7 +68621,7 @@
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T717" t="n">
@@ -68716,7 +68716,7 @@
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T718" t="n">
@@ -68811,7 +68811,7 @@
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T719" t="n">
@@ -68906,7 +68906,7 @@
       </c>
       <c r="S720" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T720" t="n">
@@ -69001,7 +69001,7 @@
       </c>
       <c r="S721" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T721" t="n">
@@ -69096,7 +69096,7 @@
       </c>
       <c r="S722" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T722" t="n">
@@ -69191,7 +69191,7 @@
       </c>
       <c r="S723" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T723" t="n">
@@ -69286,7 +69286,7 @@
       </c>
       <c r="S724" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T724" t="n">
@@ -69381,7 +69381,7 @@
       </c>
       <c r="S725" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T725" t="n">
@@ -69476,7 +69476,7 @@
       </c>
       <c r="S726" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T726" t="n">
@@ -69571,7 +69571,7 @@
       </c>
       <c r="S727" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T727" t="n">
@@ -69666,7 +69666,7 @@
       </c>
       <c r="S728" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T728" t="n">
@@ -69761,7 +69761,7 @@
       </c>
       <c r="S729" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T729" t="n">
@@ -69856,7 +69856,7 @@
       </c>
       <c r="S730" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T730" t="n">
@@ -69951,7 +69951,7 @@
       </c>
       <c r="S731" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T731" t="n">
@@ -70046,7 +70046,7 @@
       </c>
       <c r="S732" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T732" t="n">
@@ -70141,7 +70141,7 @@
       </c>
       <c r="S733" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T733" t="n">
@@ -70236,7 +70236,7 @@
       </c>
       <c r="S734" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T734" t="n">
@@ -70331,7 +70331,7 @@
       </c>
       <c r="S735" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T735" t="n">
@@ -70426,7 +70426,7 @@
       </c>
       <c r="S736" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T736" t="n">
@@ -70521,7 +70521,7 @@
       </c>
       <c r="S737" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T737" t="n">
@@ -70616,7 +70616,7 @@
       </c>
       <c r="S738" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T738" t="n">
@@ -70711,7 +70711,7 @@
       </c>
       <c r="S739" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T739" t="n">
@@ -70806,7 +70806,7 @@
       </c>
       <c r="S740" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T740" t="n">
@@ -70901,7 +70901,7 @@
       </c>
       <c r="S741" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T741" t="n">
@@ -70996,7 +70996,7 @@
       </c>
       <c r="S742" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T742" t="n">
@@ -71091,7 +71091,7 @@
       </c>
       <c r="S743" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T743" t="inlineStr"/>
@@ -71184,7 +71184,7 @@
       </c>
       <c r="S744" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T744" t="inlineStr"/>
@@ -71277,7 +71277,7 @@
       </c>
       <c r="S745" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T745" t="inlineStr"/>
@@ -71370,7 +71370,7 @@
       </c>
       <c r="S746" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T746" t="n">
@@ -71465,7 +71465,7 @@
       </c>
       <c r="S747" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T747" t="n">
@@ -71560,7 +71560,7 @@
       </c>
       <c r="S748" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T748" t="n">
@@ -71655,7 +71655,7 @@
       </c>
       <c r="S749" t="inlineStr">
         <is>
-          <t>08-07-2021 08:30</t>
+          <t>2021-08-07 08:30:00</t>
         </is>
       </c>
       <c r="T749" t="n">
@@ -71750,7 +71750,7 @@
       </c>
       <c r="S750" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T750" t="n">
@@ -71845,7 +71845,7 @@
       </c>
       <c r="S751" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T751" t="n">
@@ -71940,7 +71940,7 @@
       </c>
       <c r="S752" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T752" t="n">
@@ -72035,7 +72035,7 @@
       </c>
       <c r="S753" t="inlineStr">
         <is>
-          <t>09-12-2021 08:30</t>
+          <t>2021-09-12 08:30:00</t>
         </is>
       </c>
       <c r="T753" t="n">
@@ -72130,7 +72130,7 @@
       </c>
       <c r="S754" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T754" t="n">
@@ -72225,7 +72225,7 @@
       </c>
       <c r="S755" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T755" t="n">
@@ -72320,7 +72320,7 @@
       </c>
       <c r="S756" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T756" t="n">
@@ -72415,7 +72415,7 @@
       </c>
       <c r="S757" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T757" t="n">
@@ -72510,7 +72510,7 @@
       </c>
       <c r="S758" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T758" t="n">
@@ -72605,7 +72605,7 @@
       </c>
       <c r="S759" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T759" t="n">
@@ -72700,7 +72700,7 @@
       </c>
       <c r="S760" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T760" t="n">
@@ -72795,7 +72795,7 @@
       </c>
       <c r="S761" t="inlineStr">
         <is>
-          <t>04-09-2021 08:30</t>
+          <t>2021-04-09 08:30:00</t>
         </is>
       </c>
       <c r="T761" t="n">
@@ -72890,7 +72890,7 @@
       </c>
       <c r="S762" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T762" t="n">
@@ -72985,7 +72985,7 @@
       </c>
       <c r="S763" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T763" t="n">
@@ -73080,7 +73080,7 @@
       </c>
       <c r="S764" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T764" t="n">
@@ -73175,7 +73175,7 @@
       </c>
       <c r="S765" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T765" t="n">
@@ -73270,7 +73270,7 @@
       </c>
       <c r="S766" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T766" t="n">
@@ -73365,7 +73365,7 @@
       </c>
       <c r="S767" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T767" t="n">
@@ -73460,7 +73460,7 @@
       </c>
       <c r="S768" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T768" t="n">
@@ -73555,7 +73555,7 @@
       </c>
       <c r="S769" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T769" t="inlineStr"/>
@@ -73648,7 +73648,7 @@
       </c>
       <c r="S770" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T770" t="inlineStr"/>
@@ -73741,7 +73741,7 @@
       </c>
       <c r="S771" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T771" t="inlineStr"/>
@@ -73834,7 +73834,7 @@
       </c>
       <c r="S772" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T772" t="n">
@@ -73929,7 +73929,7 @@
       </c>
       <c r="S773" t="inlineStr">
         <is>
-          <t>04-02-2021 08:30</t>
+          <t>2021-04-02 08:30:00</t>
         </is>
       </c>
       <c r="T773" t="n">
@@ -74024,7 +74024,7 @@
       </c>
       <c r="S774" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T774" t="n">
@@ -74119,7 +74119,7 @@
       </c>
       <c r="S775" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T775" t="n">
@@ -74214,7 +74214,7 @@
       </c>
       <c r="S776" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T776" t="n">
@@ -74309,7 +74309,7 @@
       </c>
       <c r="S777" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T777" t="n">
@@ -74404,7 +74404,7 @@
       </c>
       <c r="S778" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T778" t="n">
@@ -74499,7 +74499,7 @@
       </c>
       <c r="S779" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T779" t="n">
@@ -74594,7 +74594,7 @@
       </c>
       <c r="S780" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T780" t="n">
@@ -74689,7 +74689,7 @@
       </c>
       <c r="S781" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T781" t="n">
@@ -74784,7 +74784,7 @@
       </c>
       <c r="S782" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T782" t="n">
@@ -74879,7 +74879,7 @@
       </c>
       <c r="S783" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T783" t="n">
@@ -74980,7 +74980,7 @@
       </c>
       <c r="S784" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T784" t="n">
@@ -75081,7 +75081,7 @@
       </c>
       <c r="S785" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T785" t="n">
@@ -75182,7 +75182,7 @@
       </c>
       <c r="S786" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T786" t="n">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="S787" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T787" t="n">
@@ -75378,7 +75378,7 @@
       </c>
       <c r="S788" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T788" t="n">
@@ -75473,7 +75473,7 @@
       </c>
       <c r="S789" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T789" t="n">
@@ -75568,7 +75568,7 @@
       </c>
       <c r="S790" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T790" t="n">
@@ -75663,7 +75663,7 @@
       </c>
       <c r="S791" t="inlineStr">
         <is>
-          <t>10-05-2021 08:30</t>
+          <t>2021-10-05 08:30:00</t>
         </is>
       </c>
       <c r="T791" t="n">
@@ -75758,7 +75758,7 @@
       </c>
       <c r="S792" t="inlineStr">
         <is>
-          <t>10-06-2021 08:30</t>
+          <t>2021-10-06 08:30:00</t>
         </is>
       </c>
       <c r="T792" t="n">
@@ -75853,7 +75853,7 @@
       </c>
       <c r="S793" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T793" t="n">
@@ -75948,7 +75948,7 @@
       </c>
       <c r="S794" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T794" t="n">
@@ -76043,7 +76043,7 @@
       </c>
       <c r="S795" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T795" t="n">
@@ -76138,7 +76138,7 @@
       </c>
       <c r="S796" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T796" t="n">
@@ -76233,7 +76233,7 @@
       </c>
       <c r="S797" t="inlineStr">
         <is>
-          <t>04-12-2021 08:30</t>
+          <t>2021-04-12 08:30:00</t>
         </is>
       </c>
       <c r="T797" t="n">
@@ -76328,7 +76328,7 @@
       </c>
       <c r="S798" t="inlineStr">
         <is>
-          <t>02-01-2021 08:30</t>
+          <t>2021-02-01 08:30:00</t>
         </is>
       </c>
       <c r="T798" t="n">
@@ -76423,7 +76423,7 @@
       </c>
       <c r="S799" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T799" t="inlineStr"/>
@@ -76516,7 +76516,7 @@
       </c>
       <c r="S800" t="inlineStr">
         <is>
-          <t>06-03-2021 08:30</t>
+          <t>2021-06-03 08:30:00</t>
         </is>
       </c>
       <c r="T800" t="n">
@@ -76611,7 +76611,7 @@
       </c>
       <c r="S801" t="inlineStr">
         <is>
-          <t>01-04-2021 08:30</t>
+          <t>2021-01-04 08:30:00</t>
         </is>
       </c>
       <c r="T801" t="n">
@@ -76706,7 +76706,7 @@
       </c>
       <c r="S802" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T802" t="n">
@@ -76801,7 +76801,7 @@
       </c>
       <c r="S803" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T803" t="n">
@@ -76896,7 +76896,7 @@
       </c>
       <c r="S804" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T804" t="n">
@@ -76991,7 +76991,7 @@
       </c>
       <c r="S805" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T805" t="n">
@@ -77086,7 +77086,7 @@
       </c>
       <c r="S806" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T806" t="n">
@@ -77181,7 +77181,7 @@
       </c>
       <c r="S807" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T807" t="n">
@@ -77276,7 +77276,7 @@
       </c>
       <c r="S808" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T808" t="n">
@@ -77371,7 +77371,7 @@
       </c>
       <c r="S809" t="inlineStr">
         <is>
-          <t>30-01-2021 08:30</t>
+          <t>2021-01-30 08:30:00</t>
         </is>
       </c>
       <c r="T809" t="n">
@@ -77466,7 +77466,7 @@
       </c>
       <c r="S810" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T810" t="n">
@@ -77561,7 +77561,7 @@
       </c>
       <c r="S811" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T811" t="n">
@@ -77656,7 +77656,7 @@
       </c>
       <c r="S812" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T812" t="n">
@@ -77751,7 +77751,7 @@
       </c>
       <c r="S813" t="inlineStr">
         <is>
-          <t>06-05-2021 08:30</t>
+          <t>2021-06-05 08:30:00</t>
         </is>
       </c>
       <c r="T813" t="n">
@@ -77846,7 +77846,7 @@
       </c>
       <c r="S814" t="inlineStr">
         <is>
-          <t>28-06-2021 08:30</t>
+          <t>2021-06-28 08:30:00</t>
         </is>
       </c>
       <c r="T814" t="n">
@@ -77941,7 +77941,7 @@
       </c>
       <c r="S815" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T815" t="n">
@@ -78036,7 +78036,7 @@
       </c>
       <c r="S816" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T816" t="n">
@@ -78131,7 +78131,7 @@
       </c>
       <c r="S817" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T817" t="n">
